--- a/measurement_data/firefox/memory_firefox.xlsx
+++ b/measurement_data/firefox/memory_firefox.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e934821de9c4637b/Dilons-Files/School-files/University/Webbutveckling/Vår-2026-Termin/Examensarbete-i-informationsteknologi-med-inriktning-mot-webbprogrammering-G2E-2026/final/finalData2/firefox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="969" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{682BF5DF-0966-403F-9074-137CF6FBD22D}"/>
+  <xr:revisionPtr revIDLastSave="983" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BE0B549-C0F7-49A6-85C3-9D25EC3F8E6D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,18 +113,9 @@
     <t>Rust ArrayBuffer % of Total Average</t>
   </si>
   <si>
-    <t>Heap without ArrayBuffer (MB)</t>
-  </si>
-  <si>
     <t>Total Average Heap without ArrayBuffer (MB)</t>
   </si>
   <si>
-    <t>C++ Heap without ArrayBuffer (MB)</t>
-  </si>
-  <si>
-    <t>Rust Heap without ArrayBuffer (MB)</t>
-  </si>
-  <si>
     <t>C++ in Firefox memory 2000 particles:</t>
   </si>
   <si>
@@ -153,6 +144,15 @@
   </si>
   <si>
     <t>Rust in Firefox memory 10000 particles:</t>
+  </si>
+  <si>
+    <t>Heap without ArrayBuffer Size (MB)</t>
+  </si>
+  <si>
+    <t>C++ Heap without ArrayBuffer Size (MB)</t>
+  </si>
+  <si>
+    <t>Rust Heap without ArrayBuffer Size (MB)</t>
   </si>
 </sst>
 </file>
@@ -380,7 +380,7 @@
     <tableColumn id="1" xr3:uid="{6ABC1957-5D03-4118-A03C-55CCE0A3DE17}" name="Snapshot"/>
     <tableColumn id="2" xr3:uid="{C29B1912-3DB5-4BB5-9535-F5469ACDB739}" name="ArrayBuffer Size (MB)"/>
     <tableColumn id="3" xr3:uid="{B06ABBBF-2733-456A-859D-C7556E164CFB}" name="Total Heap Memory (MB)"/>
-    <tableColumn id="7" xr3:uid="{D6FE7018-D634-4D7F-A0C0-3CD1A50204FF}" name="Heap without ArrayBuffer (MB)" dataDxfId="19">
+    <tableColumn id="7" xr3:uid="{D6FE7018-D634-4D7F-A0C0-3CD1A50204FF}" name="Heap without ArrayBuffer Size (MB)" dataDxfId="19">
       <calculatedColumnFormula>C3-B3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{8E33240B-A404-4128-A937-1F80A6B01AD8}" name="ArrayBuffer % of Total"/>
@@ -396,7 +396,7 @@
     <tableColumn id="1" xr3:uid="{D0FA21B0-97AE-4607-B500-41E3C925382A}" name="Snapshot"/>
     <tableColumn id="2" xr3:uid="{71DB07DF-A1DC-4A5E-B9E4-A685C2F3E18A}" name="ArrayBuffer Size (MB)"/>
     <tableColumn id="3" xr3:uid="{A81F1006-7727-45B9-A045-18E4F600759A}" name="Total Heap Memory (MB)"/>
-    <tableColumn id="5" xr3:uid="{38D2F5FF-319C-4C1E-A014-5D03C42F05FA}" name="Heap without ArrayBuffer (MB)" dataDxfId="10">
+    <tableColumn id="5" xr3:uid="{38D2F5FF-319C-4C1E-A014-5D03C42F05FA}" name="Heap without ArrayBuffer Size (MB)" dataDxfId="10">
       <calculatedColumnFormula>AA14-Z14</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{B79D5D7E-2DF3-4653-AA76-491305497369}" name="ArrayBuffer % of Total"/>
@@ -446,8 +446,8 @@
   <autoFilter ref="M24:O29" xr:uid="{54C81C4C-8144-4929-A814-8641FDF16C42}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{99230999-5134-4660-8552-2D4C16D1FAD7}" name="Particles"/>
-    <tableColumn id="2" xr3:uid="{470C9E9C-1B9A-4B71-B5A0-31E80B849928}" name="C++ Heap without ArrayBuffer (MB)" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{F0EA3D17-17C7-475C-9464-1B81B4F764C1}" name="Rust Heap without ArrayBuffer (MB)"/>
+    <tableColumn id="2" xr3:uid="{470C9E9C-1B9A-4B71-B5A0-31E80B849928}" name="C++ Heap without ArrayBuffer Size (MB)" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{F0EA3D17-17C7-475C-9464-1B81B4F764C1}" name="Rust Heap without ArrayBuffer Size (MB)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -460,7 +460,7 @@
     <tableColumn id="1" xr3:uid="{DB0B34B2-A771-43A8-BF7C-4E8C82163494}" name="Snapshot"/>
     <tableColumn id="2" xr3:uid="{3268860B-CE87-4580-B12C-F5867B0FF60B}" name="ArrayBuffer Size (MB)"/>
     <tableColumn id="3" xr3:uid="{7A68249E-0D96-4E9C-BF1E-08474D8CC54C}" name="Total Heap Memory (MB)"/>
-    <tableColumn id="5" xr3:uid="{874BC66A-24C5-46BB-92F9-F3D5AD8DD747}" name="Heap without ArrayBuffer (MB)" dataDxfId="18">
+    <tableColumn id="5" xr3:uid="{874BC66A-24C5-46BB-92F9-F3D5AD8DD747}" name="Heap without ArrayBuffer Size (MB)" dataDxfId="18">
       <calculatedColumnFormula>I3-H3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{491FE388-B265-4B48-AC31-32E6C0D8492E}" name="ArrayBuffer % of Total"/>
@@ -476,7 +476,7 @@
     <tableColumn id="1" xr3:uid="{51EAAC3B-9532-4437-8639-FAA50E24E13D}" name="Snapshot"/>
     <tableColumn id="2" xr3:uid="{38AEF164-5EA8-46BF-AB9F-9E13CAC3E4E7}" name="ArrayBuffer Size (MB)"/>
     <tableColumn id="3" xr3:uid="{EB620C95-B460-4304-89D5-4FDFD67E2D65}" name="Total Heap Memory (MB)"/>
-    <tableColumn id="5" xr3:uid="{3397C3CC-A3D8-425D-8507-B5A8333B292F}" name="Heap without ArrayBuffer (MB)" dataDxfId="17">
+    <tableColumn id="5" xr3:uid="{3397C3CC-A3D8-425D-8507-B5A8333B292F}" name="Heap without ArrayBuffer Size (MB)" dataDxfId="17">
       <calculatedColumnFormula>O3-N3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{CE403B80-A94F-4295-AC5D-A9F674C96E6B}" name="ArrayBuffer % of Total"/>
@@ -492,7 +492,7 @@
     <tableColumn id="1" xr3:uid="{8618A578-2D41-4A69-A340-256E3BA2C41E}" name="Snapshot"/>
     <tableColumn id="2" xr3:uid="{DE28EB2C-E89C-47E8-9B2E-4E211ED7B23C}" name="ArrayBuffer Size (MB)"/>
     <tableColumn id="3" xr3:uid="{5F1C7BF4-5E44-45E5-94FA-CA0D56F893F6}" name="Total Heap Memory (MB)"/>
-    <tableColumn id="5" xr3:uid="{F595B5D3-F528-4A25-A96C-89010A03DC66}" name="Heap without ArrayBuffer (MB)" dataDxfId="16">
+    <tableColumn id="5" xr3:uid="{F595B5D3-F528-4A25-A96C-89010A03DC66}" name="Heap without ArrayBuffer Size (MB)" dataDxfId="16">
       <calculatedColumnFormula>U3-T3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{70F71FE1-F06B-45FD-B60B-C694BC111572}" name="ArrayBuffer % of Total"/>
@@ -508,7 +508,7 @@
     <tableColumn id="1" xr3:uid="{0D31ED94-CBC9-4A04-A3CD-74D104B10543}" name="Snapshot"/>
     <tableColumn id="2" xr3:uid="{E4B1BBB1-6488-4536-B7AD-7D5D7B1E2D37}" name="ArrayBuffer Size (MB)"/>
     <tableColumn id="3" xr3:uid="{0CE4D948-4955-466B-9383-536EC451C47E}" name="Total Heap Memory (MB)"/>
-    <tableColumn id="5" xr3:uid="{5A554346-68E4-4428-9491-C546963F7364}" name="Heap without ArrayBuffer (MB)" dataDxfId="15">
+    <tableColumn id="5" xr3:uid="{5A554346-68E4-4428-9491-C546963F7364}" name="Heap without ArrayBuffer Size (MB)" dataDxfId="15">
       <calculatedColumnFormula>AA3-Z3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{E2A75BCD-9C32-499E-8941-147A405E794A}" name="ArrayBuffer % of Total"/>
@@ -524,7 +524,7 @@
     <tableColumn id="1" xr3:uid="{C4D0472B-C216-456B-9131-E909A8FFC856}" name="Snapshot"/>
     <tableColumn id="2" xr3:uid="{BA48BEE8-36F2-4960-A109-70D736A0B1F9}" name="ArrayBuffer Size (MB)"/>
     <tableColumn id="3" xr3:uid="{BD8AD3A9-FA88-4E0A-BF50-576499CAF1DA}" name="Total Heap Memory (MB)"/>
-    <tableColumn id="5" xr3:uid="{9060AC1A-0D05-46E6-9E39-678BD8E6C4D2}" name="Heap without ArrayBuffer (MB)" dataDxfId="14">
+    <tableColumn id="5" xr3:uid="{9060AC1A-0D05-46E6-9E39-678BD8E6C4D2}" name="Heap without ArrayBuffer Size (MB)" dataDxfId="14">
       <calculatedColumnFormula>C14-B14</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{AD7D8484-446E-4799-9EBB-5D17877F803E}" name="ArrayBuffer % of Total"/>
@@ -540,7 +540,7 @@
     <tableColumn id="1" xr3:uid="{A02D8CC5-B368-4373-868C-961DE4CEF912}" name="Snapshot"/>
     <tableColumn id="2" xr3:uid="{8B08D925-C811-43A9-8D8B-433EE10791D7}" name="ArrayBuffer Size (MB)"/>
     <tableColumn id="3" xr3:uid="{76E76AC9-BEB3-495A-B72C-0BDD1FCCC670}" name="Total Heap Memory (MB)"/>
-    <tableColumn id="5" xr3:uid="{FBAC7B55-1C8B-44E4-AF6C-B38F886A6175}" name="Heap without ArrayBuffer (MB)" dataDxfId="13">
+    <tableColumn id="5" xr3:uid="{FBAC7B55-1C8B-44E4-AF6C-B38F886A6175}" name="Heap without ArrayBuffer Size (MB)" dataDxfId="13">
       <calculatedColumnFormula>I14-H14</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{3D03B513-735D-4D75-9D71-D608E018F25E}" name="ArrayBuffer % of Total"/>
@@ -556,7 +556,7 @@
     <tableColumn id="1" xr3:uid="{76ACB473-23D6-4A63-8B9B-1069DFDF1003}" name="Snapshot"/>
     <tableColumn id="2" xr3:uid="{045CA9F9-0945-426D-94F8-80D66E898285}" name="ArrayBuffer Size (MB)"/>
     <tableColumn id="3" xr3:uid="{9E7B4DD4-826E-4E60-BFAE-093C72767A64}" name="Total Heap Memory (MB)"/>
-    <tableColumn id="5" xr3:uid="{1D82A794-537D-4480-8C49-E04EF7EA1EE2}" name="Heap without ArrayBuffer (MB)" dataDxfId="12">
+    <tableColumn id="5" xr3:uid="{1D82A794-537D-4480-8C49-E04EF7EA1EE2}" name="Heap without ArrayBuffer Size (MB)" dataDxfId="12">
       <calculatedColumnFormula>O14-N14</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{CFA3246A-CFE3-439E-BFC3-907DD7995CFB}" name="ArrayBuffer % of Total"/>
@@ -572,7 +572,7 @@
     <tableColumn id="1" xr3:uid="{7755CB6F-1545-4B2D-A4E3-F76B3109DD07}" name="Snapshot"/>
     <tableColumn id="2" xr3:uid="{D877C9A6-DD9B-4CD3-9C57-37AD730557C2}" name="ArrayBuffer Size (MB)"/>
     <tableColumn id="3" xr3:uid="{A166DCB3-4150-4401-A289-7E66305450B9}" name="Total Heap Memory (MB)"/>
-    <tableColumn id="5" xr3:uid="{01BADC5F-1F8C-4ADF-A8CE-CA64B0CB1EF7}" name="Heap without ArrayBuffer (MB)" dataDxfId="11">
+    <tableColumn id="5" xr3:uid="{01BADC5F-1F8C-4ADF-A8CE-CA64B0CB1EF7}" name="Heap without ArrayBuffer Size (MB)" dataDxfId="11">
       <calculatedColumnFormula>U14-T14</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{175310FF-2DC1-497F-84DA-33B88104F58D}" name="ArrayBuffer % of Total"/>
@@ -894,8 +894,8 @@
     <col min="11" max="11" width="39.77734375" customWidth="1"/>
     <col min="12" max="12" width="36" customWidth="1"/>
     <col min="13" max="13" width="44" customWidth="1"/>
-    <col min="14" max="14" width="35" customWidth="1"/>
-    <col min="15" max="15" width="35.109375" customWidth="1"/>
+    <col min="14" max="14" width="40" customWidth="1"/>
+    <col min="15" max="15" width="39.33203125" customWidth="1"/>
     <col min="16" max="16" width="35.77734375" customWidth="1"/>
     <col min="17" max="17" width="23.88671875" customWidth="1"/>
     <col min="18" max="18" width="25.6640625" customWidth="1"/>
@@ -914,19 +914,19 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" t="s">
+      <c r="M1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" t="s">
         <v>32</v>
       </c>
-      <c r="M1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S1" t="s">
-        <v>35</v>
-      </c>
       <c r="Y1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
@@ -940,7 +940,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -955,7 +955,7 @@
         <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K2" t="s">
         <v>13</v>
@@ -970,7 +970,7 @@
         <v>12</v>
       </c>
       <c r="P2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
         <v>13</v>
@@ -985,7 +985,7 @@
         <v>12</v>
       </c>
       <c r="V2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="W2" t="s">
         <v>13</v>
@@ -1000,7 +1000,7 @@
         <v>12</v>
       </c>
       <c r="AB2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AC2" t="s">
         <v>13</v>
@@ -1540,19 +1540,19 @@
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" t="s">
         <v>31</v>
       </c>
-      <c r="M12" t="s">
-        <v>34</v>
-      </c>
       <c r="S12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="Y12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.3">
@@ -1566,7 +1566,7 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -1581,7 +1581,7 @@
         <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K13" t="s">
         <v>13</v>
@@ -1596,7 +1596,7 @@
         <v>12</v>
       </c>
       <c r="P13" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Q13" t="s">
         <v>13</v>
@@ -1611,7 +1611,7 @@
         <v>12</v>
       </c>
       <c r="V13" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="W13" t="s">
         <v>13</v>
@@ -1626,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="AB13" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AC13" t="s">
         <v>13</v>
@@ -2175,7 +2175,7 @@
         <v>18</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.3">
@@ -2210,10 +2210,10 @@
         <v>15</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.3">
